--- a/crawler/headpagepedynamic.xlsx
+++ b/crawler/headpagepedynamic.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA376"/>
+  <dimension ref="A1:AA399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -32248,88 +32248,2043 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
+      <c r="A376" s="2" t="inlineStr">
         <is>
           <t>2026/6/29</t>
         </is>
       </c>
-      <c r="B376" t="n">
+      <c r="B376" s="2" t="n">
         <v>30.4</v>
       </c>
-      <c r="C376" t="n">
+      <c r="C376" s="2" t="n">
         <v>46.71</v>
       </c>
-      <c r="D376" t="n">
+      <c r="D376" s="2" t="n">
         <v>26.65</v>
       </c>
-      <c r="E376" t="n">
+      <c r="E376" s="2" t="n">
         <v>28.31</v>
       </c>
-      <c r="F376" t="n">
+      <c r="F376" s="2" t="n">
         <v>44.71</v>
       </c>
-      <c r="G376" t="n">
+      <c r="G376" s="2" t="n">
         <v>17.81</v>
       </c>
-      <c r="H376" t="n">
+      <c r="H376" s="2" t="n">
         <v>40.7</v>
       </c>
-      <c r="I376" t="n">
+      <c r="I376" s="2" t="n">
         <v>53.64</v>
       </c>
-      <c r="J376" t="n">
+      <c r="J376" s="2" t="n">
         <v>58.28</v>
       </c>
-      <c r="K376" t="n">
+      <c r="K376" s="2" t="n">
         <v>34.16</v>
       </c>
-      <c r="L376" t="n">
+      <c r="L376" s="2" t="n">
         <v>58.09</v>
       </c>
-      <c r="M376" t="n">
+      <c r="M376" s="2" t="n">
         <v>24.36</v>
       </c>
-      <c r="N376" t="n">
+      <c r="N376" s="2" t="n">
         <v>18.47</v>
       </c>
-      <c r="O376" t="n">
+      <c r="O376" s="2" t="n">
         <v>44.81</v>
       </c>
-      <c r="P376" t="n">
+      <c r="P376" s="2" t="n">
         <v>31.73</v>
       </c>
-      <c r="Q376" t="n">
+      <c r="Q376" s="2" t="n">
         <v>17.76</v>
       </c>
-      <c r="R376" t="n">
+      <c r="R376" s="2" t="n">
         <v>39.56</v>
       </c>
-      <c r="S376" t="n">
+      <c r="S376" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="T376" t="n">
+      <c r="T376" s="2" t="n">
         <v>142.13</v>
       </c>
-      <c r="U376" t="n">
+      <c r="U376" s="2" t="n">
         <v>24.46</v>
       </c>
-      <c r="V376" t="n">
+      <c r="V376" s="2" t="n">
         <v>28.06</v>
       </c>
-      <c r="W376" t="n">
+      <c r="W376" s="2" t="n">
         <v>16.56</v>
       </c>
-      <c r="X376" t="n">
+      <c r="X376" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="Y376" t="n">
+      <c r="Y376" s="2" t="n">
         <v>77.55</v>
       </c>
-      <c r="Z376" t="n">
+      <c r="Z376" s="2" t="n">
         <v>8.09</v>
       </c>
-      <c r="AA376" t="n">
+      <c r="AA376" s="2" t="n">
         <v>8.99</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/30</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="C377" s="2" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="D377" s="2" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="E377" s="2" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>46.01</v>
+      </c>
+      <c r="G377" s="2" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="H377" s="2" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="I377" s="2" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="J377" s="2" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="K377" s="2" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="L377" s="2" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="N377" s="2" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="O377" s="2" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="P377" s="2" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="Q377" s="2" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="R377" s="2" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="S377" s="2" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="T377" s="2" t="n">
+        <v>146.38</v>
+      </c>
+      <c r="U377" s="2" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="V377" s="2" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="W377" s="2" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="X377" s="2" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="Y377" s="2" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="Z377" s="2" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AA377" s="2" t="n">
+        <v>8.859999999999999</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/01</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="C378" s="2" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="D378" s="2" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="E378" s="2" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="G378" s="2" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="H378" s="2" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="I378" s="2" t="n">
+        <v>56.13</v>
+      </c>
+      <c r="J378" s="2" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="K378" s="2" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="L378" s="2" t="n">
+        <v>59.58</v>
+      </c>
+      <c r="M378" s="2" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="N378" s="2" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="O378" s="2" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="P378" s="2" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="Q378" s="2" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="R378" s="2" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="S378" s="2" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="T378" s="2" t="n">
+        <v>142.76</v>
+      </c>
+      <c r="U378" s="2" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="V378" s="2" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="W378" s="2" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="X378" s="2" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="Y378" s="2" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="Z378" s="2" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="AA378" s="2" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/02</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="C379" s="2" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="D379" s="2" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="E379" s="2" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="F379" s="2" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="G379" s="2" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H379" s="2" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="I379" s="2" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="J379" s="2" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="K379" s="2" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="L379" s="2" t="n">
+        <v>55.23</v>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="N379" s="2" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="O379" s="2" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="P379" s="2" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="Q379" s="2" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="R379" s="2" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="S379" s="2" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="T379" s="2" t="n">
+        <v>130.71</v>
+      </c>
+      <c r="U379" s="2" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="V379" s="2" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="W379" s="2" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="X379" s="2" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="Y379" s="2" t="n">
+        <v>73.61</v>
+      </c>
+      <c r="Z379" s="2" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="AA379" s="2" t="n">
+        <v>8.880000000000001</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/03</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="C380" s="2" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="D380" s="2" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="E380" s="2" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="F380" s="2" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="G380" s="2" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="H380" s="2" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="I380" s="2" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="J380" s="2" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="K380" s="2" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="L380" s="2" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="N380" s="2" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="O380" s="2" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="P380" s="2" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="Q380" s="2" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="R380" s="2" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="S380" s="2" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="T380" s="2" t="n">
+        <v>129.95</v>
+      </c>
+      <c r="U380" s="2" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="V380" s="2" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="W380" s="2" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="X380" s="2" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="Y380" s="2" t="n">
+        <v>74.37</v>
+      </c>
+      <c r="Z380" s="2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA380" s="2" t="n">
+        <v>8.92</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/06</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="C381" s="2" t="n">
+        <v>44.01</v>
+      </c>
+      <c r="D381" s="2" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="E381" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="F381" s="2" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="G381" s="2" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="H381" s="2" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="I381" s="2" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="J381" s="2" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="K381" s="2" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="L381" s="2" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="M381" s="2" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="N381" s="2" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="O381" s="2" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="P381" s="2" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="Q381" s="2" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="R381" s="2" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="S381" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T381" s="2" t="n">
+        <v>131.28</v>
+      </c>
+      <c r="U381" s="2" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="V381" s="2" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="W381" s="2" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="X381" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="Y381" s="2" t="n">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="Z381" s="2" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="AA381" s="2" t="n">
+        <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/07</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="C382" s="2" t="n">
+        <v>44.01</v>
+      </c>
+      <c r="D382" s="2" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="E382" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="F382" s="2" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="G382" s="2" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="H382" s="2" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="I382" s="2" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="J382" s="2" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="K382" s="2" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="L382" s="2" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="M382" s="2" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="N382" s="2" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="O382" s="2" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="P382" s="2" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="Q382" s="2" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="R382" s="2" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="S382" s="2" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T382" s="2" t="n">
+        <v>131.11</v>
+      </c>
+      <c r="U382" s="2" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="V382" s="2" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="W382" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X382" s="2" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="Y382" s="2" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="Z382" s="2" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="AA382" s="2" t="n">
+        <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/08</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="C383" s="2" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="D383" s="2" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="E383" s="2" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="F383" s="2" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="G383" s="2" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="H383" s="2" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="I383" s="2" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="J383" s="2" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="K383" s="2" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="L383" s="2" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="M383" s="2" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="N383" s="2" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="O383" s="2" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="P383" s="2" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="Q383" s="2" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="R383" s="2" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="S383" s="2" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="T383" s="2" t="n">
+        <v>130.73</v>
+      </c>
+      <c r="U383" s="2" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="V383" s="2" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="W383" s="2" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="X383" s="2" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="Y383" s="2" t="n">
+        <v>70.73</v>
+      </c>
+      <c r="Z383" s="2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="AA383" s="2" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/09</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="C384" s="2" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="D384" s="2" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="E384" s="2" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="F384" s="2" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G384" s="2" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="H384" s="2" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="I384" s="2" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="J384" s="2" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="K384" s="2" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="L384" s="2" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="M384" s="2" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N384" s="2" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="O384" s="2" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="P384" s="2" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="Q384" s="2" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="R384" s="2" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="S384" s="2" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="T384" s="2" t="n">
+        <v>142.4</v>
+      </c>
+      <c r="U384" s="2" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="V384" s="2" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="W384" s="2" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="X384" s="2" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="Y384" s="2" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="Z384" s="2" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="AA384" s="2" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/10</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="n">
+        <v>28.97</v>
+      </c>
+      <c r="C385" s="2" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="D385" s="2" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="E385" s="2" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="F385" s="2" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="G385" s="2" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="H385" s="2" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="I385" s="2" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="J385" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="K385" s="2" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="L385" s="2" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="N385" s="2" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="O385" s="2" t="n">
+        <v>40.32</v>
+      </c>
+      <c r="P385" s="2" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="Q385" s="2" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="R385" s="2" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="S385" s="2" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="T385" s="2" t="n">
+        <v>133.07</v>
+      </c>
+      <c r="U385" s="2" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="V385" s="2" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="W385" s="2" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="X385" s="2" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="Y385" s="2" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="Z385" s="2" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="AA385" s="2" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/13</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="C386" s="2" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="D386" s="2" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="E386" s="2" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F386" s="2" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="G386" s="2" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="H386" s="2" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="I386" s="2" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="J386" s="2" t="n">
+        <v>52.27</v>
+      </c>
+      <c r="K386" s="2" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="L386" s="2" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="M386" s="2" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="N386" s="2" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="O386" s="2" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="P386" s="2" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="Q386" s="2" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="R386" s="2" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="S386" s="2" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="T386" s="2" t="n">
+        <v>128.39</v>
+      </c>
+      <c r="U386" s="2" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="V386" s="2" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="W386" s="2" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="X386" s="2" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="Y386" s="2" t="n">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="Z386" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA386" s="2" t="n">
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/14</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="C387" s="2" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="D387" s="2" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="E387" s="2" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F387" s="2" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="G387" s="2" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="H387" s="2" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="I387" s="2" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="J387" s="2" t="n">
+        <v>52.27</v>
+      </c>
+      <c r="K387" s="2" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="L387" s="2" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="M387" s="2" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="N387" s="2" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="O387" s="2" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="P387" s="2" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="Q387" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="R387" s="2" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="S387" s="2" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="T387" s="2" t="n">
+        <v>130.44</v>
+      </c>
+      <c r="U387" s="2" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="V387" s="2" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="W387" s="2" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="X387" s="2" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="Y387" s="2" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="Z387" s="2" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="AA387" s="2" t="n">
+        <v>9.33</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/15</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="C388" s="2" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="D388" s="2" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="E388" s="2" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="F388" s="2" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="G388" s="2" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="H388" s="2" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="I388" s="2" t="n">
+        <v>48.39</v>
+      </c>
+      <c r="J388" s="2" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="K388" s="2" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="L388" s="2" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="M388" s="2" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="N388" s="2" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="O388" s="2" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="P388" s="2" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="Q388" s="2" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="R388" s="2" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="S388" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T388" s="2" t="n">
+        <v>123.69</v>
+      </c>
+      <c r="U388" s="2" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="V388" s="2" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="W388" s="2" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="X388" s="2" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="Y388" s="2" t="n">
+        <v>69.69</v>
+      </c>
+      <c r="Z388" s="2" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="AA388" s="2" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/16</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="C389" s="2" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="D389" s="2" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="E389" s="2" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="F389" s="2" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="G389" s="2" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H389" s="2" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="I389" s="2" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="J389" s="2" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="K389" s="2" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="L389" s="2" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="M389" s="2" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="N389" s="2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="O389" s="2" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="P389" s="2" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="Q389" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="R389" s="2" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="S389" s="2" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="T389" s="2" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="U389" s="2" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="V389" s="2" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="W389" s="2" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="X389" s="2" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="Y389" s="2" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="Z389" s="2" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="AA389" s="2" t="n">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/17</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="C390" s="2" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="D390" s="2" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="E390" s="2" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="F390" s="2" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="G390" s="2" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="H390" s="2" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="I390" s="2" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="J390" s="2" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="K390" s="2" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="L390" s="2" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="M390" s="2" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="N390" s="2" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="O390" s="2" t="n">
+        <v>35.97</v>
+      </c>
+      <c r="P390" s="2" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="Q390" s="2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="R390" s="2" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="S390" s="2" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="T390" s="2" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="U390" s="2" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="V390" s="2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W390" s="2" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="X390" s="2" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="Y390" s="2" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="Z390" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA390" s="2" t="n">
+        <v>9.34</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/20</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="C391" s="2" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="D391" s="2" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="E391" s="2" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="F391" s="2" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="G391" s="2" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="H391" s="2" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="I391" s="2" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="J391" s="2" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="K391" s="2" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="L391" s="2" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="M391" s="2" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="N391" s="2" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="O391" s="2" t="n">
+        <v>35.97</v>
+      </c>
+      <c r="P391" s="2" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="Q391" s="2" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="R391" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="S391" s="2" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="T391" s="2" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="U391" s="2" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="V391" s="2" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="W391" s="2" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="X391" s="2" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="Y391" s="2" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="Z391" s="2" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="AA391" s="2" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/21</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="C392" s="2" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="D392" s="2" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="E392" s="2" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="F392" s="2" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="G392" s="2" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="H392" s="2" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="I392" s="2" t="n">
+        <v>44.63</v>
+      </c>
+      <c r="J392" s="2" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="K392" s="2" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="L392" s="2" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="M392" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="N392" s="2" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="O392" s="2" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="P392" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q392" s="2" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="R392" s="2" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="S392" s="2" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="T392" s="2" t="n">
+        <v>119.45</v>
+      </c>
+      <c r="U392" s="2" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="V392" s="2" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="W392" s="2" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="X392" s="2" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="Y392" s="2" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="Z392" s="2" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="AA392" s="2" t="n">
+        <v>9.529999999999999</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/22</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="C393" s="2" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="D393" s="2" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="E393" s="2" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="F393" s="2" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="G393" s="2" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H393" s="2" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="I393" s="2" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="J393" s="2" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="K393" s="2" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="L393" s="2" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="M393" s="2" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="N393" s="2" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="O393" s="2" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="P393" s="2" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="Q393" s="2" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="R393" s="2" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="S393" s="2" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="T393" s="2" t="n">
+        <v>117.43</v>
+      </c>
+      <c r="U393" s="2" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="V393" s="2" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="W393" s="2" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="X393" s="2" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="Y393" s="2" t="n">
+        <v>61.11</v>
+      </c>
+      <c r="Z393" s="2" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="AA393" s="2" t="n">
+        <v>9.640000000000001</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/23</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="C394" s="2" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="D394" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E394" s="2" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="F394" s="2" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="G394" s="2" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="H394" s="2" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="I394" s="2" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="J394" s="2" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="K394" s="2" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="L394" s="2" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="M394" s="2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="N394" s="2" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="O394" s="2" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="P394" s="2" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="Q394" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R394" s="2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="S394" s="2" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="T394" s="2" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="U394" s="2" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="V394" s="2" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="W394" s="2" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="X394" s="2" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Y394" s="2" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="Z394" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA394" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/24</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="C395" s="2" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="D395" s="2" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="E395" s="2" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="G395" s="2" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I395" s="2" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="J395" s="2" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="K395" s="2" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="L395" s="2" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="M395" s="2" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="N395" s="2" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="O395" s="2" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="P395" s="2" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="Q395" s="2" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="R395" s="2" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="S395" s="2" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="T395" s="2" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="U395" s="2" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="V395" s="2" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="W395" s="2" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="X395" s="2" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="Y395" s="2" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="Z395" s="2" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AA395" s="2" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/27</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="C396" s="2" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="D396" s="2" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="E396" s="2" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="G396" s="2" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H396" s="2" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I396" s="2" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="J396" s="2" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="K396" s="2" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="L396" s="2" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="M396" s="2" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="N396" s="2" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="O396" s="2" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="P396" s="2" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="Q396" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="R396" s="2" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="S396" s="2" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="T396" s="2" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="U396" s="2" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="V396" s="2" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="W396" s="2" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="X396" s="2" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="Y396" s="2" t="n">
+        <v>61.87</v>
+      </c>
+      <c r="Z396" s="2" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AA396" s="2" t="n">
+        <v>9.67</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/28</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="C397" s="2" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="D397" s="2" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="E397" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F397" s="2" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="G397" s="2" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H397" s="2" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I397" s="2" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="J397" s="2" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="K397" s="2" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="L397" s="2" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="M397" s="2" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="N397" s="2" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="O397" s="2" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="P397" s="2" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="Q397" s="2" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="R397" s="2" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="S397" s="2" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="T397" s="2" t="n">
+        <v>105.01</v>
+      </c>
+      <c r="U397" s="2" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="V397" s="2" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="W397" s="2" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="X397" s="2" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y397" s="2" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="Z397" s="2" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="AA397" s="2" t="n">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/29</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="C398" s="2" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="D398" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E398" s="2" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G398" s="2" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="H398" s="2" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="I398" s="2" t="n">
+        <v>43.03</v>
+      </c>
+      <c r="J398" s="2" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="K398" s="2" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="L398" s="2" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="M398" s="2" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="N398" s="2" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="O398" s="2" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="P398" s="2" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="Q398" s="2" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="R398" s="2" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="S398" s="2" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="T398" s="2" t="n">
+        <v>102.71</v>
+      </c>
+      <c r="U398" s="2" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="V398" s="2" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="W398" s="2" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="X398" s="2" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="Y398" s="2" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="Z398" s="2" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="AA398" s="2" t="n">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026/7/30</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="C399" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="D399" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E399" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="F399" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G399" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="H399" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="I399" t="n">
+        <v>43.03</v>
+      </c>
+      <c r="J399" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="K399" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="L399" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="M399" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="N399" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="O399" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="P399" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="R399" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="S399" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="T399" t="n">
+        <v>102.71</v>
+      </c>
+      <c r="U399" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="V399" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="W399" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="X399" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="Y399" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="Z399" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="AA399" t="n">
+        <v>9.779999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/crawler/headpagepedynamic.xlsx
+++ b/crawler/headpagepedynamic.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA399"/>
+  <dimension ref="A1:AA420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -34203,88 +34203,1873 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
+      <c r="A399" s="2" t="inlineStr">
         <is>
           <t>2026/7/30</t>
         </is>
       </c>
-      <c r="B399" t="n">
+      <c r="B399" s="2" t="n">
         <v>26.68</v>
       </c>
-      <c r="C399" t="n">
+      <c r="C399" s="2" t="n">
         <v>37.84</v>
       </c>
-      <c r="D399" t="n">
+      <c r="D399" s="2" t="n">
         <v>24.25</v>
       </c>
-      <c r="E399" t="n">
+      <c r="E399" s="2" t="n">
         <v>26.42</v>
       </c>
-      <c r="F399" t="n">
+      <c r="F399" s="2" t="n">
         <v>35.75</v>
       </c>
-      <c r="G399" t="n">
+      <c r="G399" s="2" t="n">
         <v>18.16</v>
       </c>
-      <c r="H399" t="n">
+      <c r="H399" s="2" t="n">
         <v>35.99</v>
       </c>
-      <c r="I399" t="n">
+      <c r="I399" s="2" t="n">
         <v>43.03</v>
       </c>
-      <c r="J399" t="n">
+      <c r="J399" s="2" t="n">
         <v>46.05</v>
       </c>
-      <c r="K399" t="n">
+      <c r="K399" s="2" t="n">
         <v>29.64</v>
       </c>
-      <c r="L399" t="n">
+      <c r="L399" s="2" t="n">
         <v>46.13</v>
       </c>
-      <c r="M399" t="n">
+      <c r="M399" s="2" t="n">
         <v>22.83</v>
       </c>
-      <c r="N399" t="n">
+      <c r="N399" s="2" t="n">
         <v>18.78</v>
       </c>
-      <c r="O399" t="n">
+      <c r="O399" s="2" t="n">
         <v>35.72</v>
       </c>
-      <c r="P399" t="n">
+      <c r="P399" s="2" t="n">
         <v>28.42</v>
       </c>
-      <c r="Q399" t="n">
+      <c r="Q399" s="2" t="n">
         <v>16.68</v>
       </c>
-      <c r="R399" t="n">
+      <c r="R399" s="2" t="n">
         <v>32.98</v>
       </c>
-      <c r="S399" t="n">
+      <c r="S399" s="2" t="n">
         <v>18.66</v>
       </c>
-      <c r="T399" t="n">
+      <c r="T399" s="2" t="n">
         <v>102.71</v>
       </c>
-      <c r="U399" t="n">
+      <c r="U399" s="2" t="n">
         <v>25.12</v>
       </c>
-      <c r="V399" t="n">
+      <c r="V399" s="2" t="n">
         <v>25.81</v>
       </c>
-      <c r="W399" t="n">
+      <c r="W399" s="2" t="n">
         <v>15.79</v>
       </c>
-      <c r="X399" t="n">
+      <c r="X399" s="2" t="n">
         <v>20.03</v>
       </c>
-      <c r="Y399" t="n">
+      <c r="Y399" s="2" t="n">
         <v>56.63</v>
       </c>
-      <c r="Z399" t="n">
+      <c r="Z399" s="2" t="n">
         <v>8.92</v>
       </c>
-      <c r="AA399" t="n">
+      <c r="AA399" s="2" t="n">
         <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/31</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="C400" s="2" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="D400" s="2" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="E400" s="2" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="G400" s="2" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="H400" s="2" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I400" s="2" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="J400" s="2" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="K400" s="2" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="L400" s="2" t="n">
+        <v>45.52</v>
+      </c>
+      <c r="M400" s="2" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="N400" s="2" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="O400" s="2" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="P400" s="2" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="Q400" s="2" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="R400" s="2" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="S400" s="2" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="T400" s="2" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="U400" s="2" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="V400" s="2" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="W400" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X400" s="2" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="Y400" s="2" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="Z400" s="2" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="AA400" s="2" t="n">
+        <v>9.880000000000001</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/03</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="C401" s="2" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="D401" s="2" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="E401" s="2" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="G401" s="2" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="H401" s="2" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="I401" s="2" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="J401" s="2" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="K401" s="2" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="L401" s="2" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="M401" s="2" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="N401" s="2" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="O401" s="2" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="P401" s="2" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="Q401" s="2" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="R401" s="2" t="n">
+        <v>32.94</v>
+      </c>
+      <c r="S401" s="2" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="T401" s="2" t="n">
+        <v>92.61</v>
+      </c>
+      <c r="U401" s="2" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="V401" s="2" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="W401" s="2" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="X401" s="2" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="Y401" s="2" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="Z401" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA401" s="2" t="n">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/04</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="C402" s="2" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="D402" s="2" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="E402" s="2" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="G402" s="2" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="H402" s="2" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I402" s="2" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="J402" s="2" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="K402" s="2" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="L402" s="2" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="M402" s="2" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="N402" s="2" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="O402" s="2" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="P402" s="2" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="Q402" s="2" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="R402" s="2" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="S402" s="2" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="T402" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="U402" s="2" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="V402" s="2" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="W402" s="2" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="X402" s="2" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="Y402" s="2" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="Z402" s="2" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AA402" s="2" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/05</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="G403" s="2" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="I403" s="2" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="J403" s="2" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="K403" s="2" t="n">
+        <v>30.37</v>
+      </c>
+      <c r="L403" s="2" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="M403" s="2" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="N403" s="2" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="O403" s="2" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="P403" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="Q403" s="2" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="R403" s="2" t="n">
+        <v>34.81</v>
+      </c>
+      <c r="S403" s="2" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="T403" s="2" t="n">
+        <v>103.53</v>
+      </c>
+      <c r="U403" s="2" t="n">
+        <v>26.87</v>
+      </c>
+      <c r="V403" s="2" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="W403" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="X403" s="2" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="Y403" s="2" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="Z403" s="2" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AA403" s="2" t="n">
+        <v>9.609999999999999</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/06</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F404" s="2" t="n">
+        <v>37.01</v>
+      </c>
+      <c r="G404" s="2" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="H404" s="2" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="I404" s="2" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="J404" s="2" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="K404" s="2" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="L404" s="2" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="M404" s="2" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="N404" s="2" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="O404" s="2" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="P404" s="2" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="Q404" s="2" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="R404" s="2" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="S404" s="2" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="T404" s="2" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="U404" s="2" t="n">
+        <v>26.23</v>
+      </c>
+      <c r="V404" s="2" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="W404" s="2" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="X404" s="2" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="Y404" s="2" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="Z404" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA404" s="2" t="n">
+        <v>9.67</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/07</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="C405" s="2" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="D405" s="2" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="G405" s="2" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="H405" s="2" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="I405" s="2" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="J405" s="2" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="K405" s="2" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="L405" s="2" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="M405" s="2" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="N405" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O405" s="2" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="P405" s="2" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="Q405" s="2" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="R405" s="2" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="S405" s="2" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="T405" s="2" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="U405" s="2" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="V405" s="2" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="W405" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X405" s="2" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="Y405" s="2" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="Z405" s="2" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AA405" s="2" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/10</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="C406" s="2" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="D406" s="2" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="E406" s="2" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="G406" s="2" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="H406" s="2" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="I406" s="2" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="J406" s="2" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="K406" s="2" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="L406" s="2" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="M406" s="2" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="N406" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O406" s="2" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="P406" s="2" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="Q406" s="2" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="R406" s="2" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="S406" s="2" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="T406" s="2" t="n">
+        <v>107.13</v>
+      </c>
+      <c r="U406" s="2" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="V406" s="2" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="W406" s="2" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="X406" s="2" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="Y406" s="2" t="n">
+        <v>82.73</v>
+      </c>
+      <c r="Z406" s="2" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AA406" s="2" t="n">
+        <v>9.74</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/11</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="C407" s="2" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="D407" s="2" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="F407" s="2" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="G407" s="2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="H407" s="2" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="I407" s="2" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="J407" s="2" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="K407" s="2" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="L407" s="2" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="M407" s="2" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="N407" s="2" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="O407" s="2" t="n">
+        <v>37.24</v>
+      </c>
+      <c r="P407" s="2" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="Q407" s="2" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="R407" s="2" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="S407" s="2" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="T407" s="2" t="n">
+        <v>105.26</v>
+      </c>
+      <c r="U407" s="2" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="V407" s="2" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="W407" s="2" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="X407" s="2" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="Y407" s="2" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="Z407" s="2" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AA407" s="2" t="n">
+        <v>9.710000000000001</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/12</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="C408" s="2" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="D408" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="F408" s="2" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="G408" s="2" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="H408" s="2" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="I408" s="2" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="J408" s="2" t="n">
+        <v>52.12</v>
+      </c>
+      <c r="K408" s="2" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="L408" s="2" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="M408" s="2" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="N408" s="2" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="O408" s="2" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="P408" s="2" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="Q408" s="2" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="R408" s="2" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="S408" s="2" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="T408" s="2" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="U408" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="V408" s="2" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="W408" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X408" s="2" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="Y408" s="2" t="n">
+        <v>83.18000000000001</v>
+      </c>
+      <c r="Z408" s="2" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="AA408" s="2" t="n">
+        <v>9.630000000000001</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/13</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="n">
+        <v>27.873</v>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>40.3899</v>
+      </c>
+      <c r="D409" s="2" t="n">
+        <v>24.8165</v>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>26.7308</v>
+      </c>
+      <c r="F409" s="2" t="n">
+        <v>37.6477</v>
+      </c>
+      <c r="G409" s="2" t="n">
+        <v>18.0653</v>
+      </c>
+      <c r="H409" s="2" t="n">
+        <v>37.2286</v>
+      </c>
+      <c r="I409" s="2" t="n">
+        <v>47.603</v>
+      </c>
+      <c r="J409" s="2" t="n">
+        <v>51.5051</v>
+      </c>
+      <c r="K409" s="2" t="n">
+        <v>30.5599</v>
+      </c>
+      <c r="L409" s="2" t="n">
+        <v>49.1846</v>
+      </c>
+      <c r="M409" s="2" t="n">
+        <v>23.0265</v>
+      </c>
+      <c r="N409" s="2" t="n">
+        <v>18.8585</v>
+      </c>
+      <c r="O409" s="2" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="P409" s="2" t="n">
+        <v>29.0872</v>
+      </c>
+      <c r="Q409" s="2" t="n">
+        <v>17.0142</v>
+      </c>
+      <c r="R409" s="2" t="n">
+        <v>35.9166</v>
+      </c>
+      <c r="S409" s="2" t="n">
+        <v>19.3073</v>
+      </c>
+      <c r="T409" s="2" t="n">
+        <v>105.7523</v>
+      </c>
+      <c r="U409" s="2" t="n">
+        <v>29.0972</v>
+      </c>
+      <c r="V409" s="2" t="n">
+        <v>26.4181</v>
+      </c>
+      <c r="W409" s="2" t="n">
+        <v>16.0156</v>
+      </c>
+      <c r="X409" s="2" t="n">
+        <v>20.6286</v>
+      </c>
+      <c r="Y409" s="2" t="n">
+        <v>82.7641</v>
+      </c>
+      <c r="Z409" s="2" t="n">
+        <v>8.753</v>
+      </c>
+      <c r="AA409" s="2" t="n">
+        <v>9.649800000000001</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/14</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="C410" s="2" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="D410" s="2" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F410" s="2" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="G410" s="2" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H410" s="2" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="I410" s="2" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="J410" s="2" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="K410" s="2" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="L410" s="2" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="M410" s="2" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="N410" s="2" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="O410" s="2" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="P410" s="2" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="Q410" s="2" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="R410" s="2" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="S410" s="2" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="T410" s="2" t="n">
+        <v>106.27</v>
+      </c>
+      <c r="U410" s="2" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="V410" s="2" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="W410" s="2" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="X410" s="2" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="Y410" s="2" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="Z410" s="2" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="AA410" s="2" t="n">
+        <v>9.609999999999999</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/17</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="C411" s="2" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="D411" s="2" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="F411" s="2" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G411" s="2" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="H411" s="2" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="I411" s="2" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J411" s="2" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="K411" s="2" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="L411" s="2" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="M411" s="2" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="N411" s="2" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="O411" s="2" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="P411" s="2" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="Q411" s="2" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="R411" s="2" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="S411" s="2" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="T411" s="2" t="n">
+        <v>111.33</v>
+      </c>
+      <c r="U411" s="2" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="V411" s="2" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="W411" s="2" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="X411" s="2" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Y411" s="2" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="Z411" s="2" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="AA411" s="2" t="n">
+        <v>9.609999999999999</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/18</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="C412" s="2" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="D412" s="2" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="E412" s="2" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="F412" s="2" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="G412" s="2" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="I412" s="2" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="J412" s="2" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="K412" s="2" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="L412" s="2" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="M412" s="2" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="N412" s="2" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="O412" s="2" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="P412" s="2" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="Q412" s="2" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="R412" s="2" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="S412" s="2" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>111.48</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="V412" s="2" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="W412" s="2" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="X412" s="2" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="Y412" s="2" t="n">
+        <v>86.41</v>
+      </c>
+      <c r="Z412" s="2" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AA412" s="2" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/19</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="C413" s="2" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="D413" s="2" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="E413" s="2" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="F413" s="2" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="G413" s="2" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="I413" s="2" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="J413" s="2" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="K413" s="2" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="L413" s="2" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="M413" s="2" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="O413" s="2" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="P413" s="2" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="Q413" s="2" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="R413" s="2" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="S413" s="2" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>102.73</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="V413" s="2" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="W413" s="2" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="X413" s="2" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="Y413" s="2" t="n">
+        <v>80.17</v>
+      </c>
+      <c r="Z413" s="2" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AA413" s="2" t="n">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="C414" s="2" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="D414" s="2" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="E414" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F414" s="2" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="G414" s="2" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="I414" s="2" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="J414" s="2" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="K414" s="2" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="L414" s="2" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="M414" s="2" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O414" s="2" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="P414" s="2" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="Q414" s="2" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="R414" s="2" t="n">
+        <v>35.41</v>
+      </c>
+      <c r="S414" s="2" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="V414" s="2" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="W414" s="2" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="X414" s="2" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="Y414" s="2" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="Z414" s="2" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AA414" s="2" t="n">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/21</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="C415" s="2" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D415" s="2" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="E415" s="2" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="F415" s="2" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="G415" s="2" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="I415" s="2" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="J415" s="2" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="K415" s="2" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="L415" s="2" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="M415" s="2" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="O415" s="2" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="P415" s="2" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="Q415" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="R415" s="2" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="S415" s="2" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>102.03</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="V415" s="2" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="W415" s="2" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="X415" s="2" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Y415" s="2" t="n">
+        <v>81.39</v>
+      </c>
+      <c r="Z415" s="2" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="AA415" s="2" t="n">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/24</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="C416" s="2" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="D416" s="2" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="E416" s="2" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="F416" s="2" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="G416" s="2" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="I416" s="2" t="n">
+        <v>45.67</v>
+      </c>
+      <c r="J416" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="K416" s="2" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="L416" s="2" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="M416" s="2" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="O416" s="2" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="P416" s="2" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="Q416" s="2" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="R416" s="2" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="S416" s="2" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="V416" s="2" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="W416" s="2" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="X416" s="2" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="Y416" s="2" t="n">
+        <v>78.45999999999999</v>
+      </c>
+      <c r="Z416" s="2" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="AA416" s="2" t="n">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/25</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="C417" s="2" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="D417" s="2" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="F417" s="2" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="G417" s="2" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="H417" s="2" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="I417" s="2" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="J417" s="2" t="n">
+        <v>50.58</v>
+      </c>
+      <c r="K417" s="2" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="L417" s="2" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="M417" s="2" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="N417" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="O417" s="2" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="P417" s="2" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="Q417" s="2" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="R417" s="2" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="S417" s="2" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="T417" s="2" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="U417" s="2" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="V417" s="2" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="W417" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X417" s="2" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="Y417" s="2" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="Z417" s="2" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="AA417" s="2" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/26</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="C418" s="2" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="D418" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E418" s="2" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="F418" s="2" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="G418" s="2" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H418" s="2" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="I418" s="2" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J418" s="2" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="K418" s="2" t="n">
+        <v>29.54</v>
+      </c>
+      <c r="L418" s="2" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="M418" s="2" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="N418" s="2" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="O418" s="2" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="P418" s="2" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="Q418" s="2" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="R418" s="2" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="S418" s="2" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="T418" s="2" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="U418" s="2" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="V418" s="2" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="W418" s="2" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="X418" s="2" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Y418" s="2" t="n">
+        <v>79.48999999999999</v>
+      </c>
+      <c r="Z418" s="2" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="AA418" s="2" t="n">
+        <v>9.869999999999999</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/27</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="C419" s="2" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="D419" s="2" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="E419" s="2" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="F419" s="2" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="G419" s="2" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="H419" s="2" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="I419" s="2" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="J419" s="2" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="K419" s="2" t="n">
+        <v>29.78</v>
+      </c>
+      <c r="L419" s="2" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="M419" s="2" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="N419" s="2" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="O419" s="2" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="P419" s="2" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="Q419" s="2" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="R419" s="2" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="S419" s="2" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="T419" s="2" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="U419" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="V419" s="2" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="W419" s="2" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="X419" s="2" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="Y419" s="2" t="n">
+        <v>82.43000000000001</v>
+      </c>
+      <c r="Z419" s="2" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AA419" s="2" t="n">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026/8/28</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="C420" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="D420" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="E420" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="F420" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="G420" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="H420" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="I420" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="J420" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="K420" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="L420" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="M420" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="N420" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="O420" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="P420" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="R420" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="S420" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="T420" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="U420" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="V420" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="W420" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="X420" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="Y420" t="n">
+        <v>81.59</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AA420" t="n">
+        <v>9.880000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/crawler/headpagepedynamic.xlsx
+++ b/crawler/headpagepedynamic.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA420"/>
+  <dimension ref="A1:AA441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -35988,88 +35988,1873 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
+      <c r="A420" s="2" t="inlineStr">
         <is>
           <t>2026/8/28</t>
         </is>
       </c>
-      <c r="B420" t="n">
+      <c r="B420" s="2" t="n">
         <v>27.31</v>
       </c>
-      <c r="C420" t="n">
+      <c r="C420" s="2" t="n">
         <v>38.6</v>
       </c>
-      <c r="D420" t="n">
+      <c r="D420" s="2" t="n">
         <v>24.27</v>
       </c>
-      <c r="E420" t="n">
+      <c r="E420" s="2" t="n">
         <v>25.64</v>
       </c>
-      <c r="F420" t="n">
+      <c r="F420" s="2" t="n">
         <v>36.02</v>
       </c>
-      <c r="G420" t="n">
+      <c r="G420" s="2" t="n">
         <v>17.99</v>
       </c>
-      <c r="H420" t="n">
+      <c r="H420" s="2" t="n">
         <v>35.74</v>
       </c>
-      <c r="I420" t="n">
+      <c r="I420" s="2" t="n">
         <v>46.85</v>
       </c>
-      <c r="J420" t="n">
+      <c r="J420" s="2" t="n">
         <v>51.22</v>
       </c>
-      <c r="K420" t="n">
+      <c r="K420" s="2" t="n">
         <v>29.47</v>
       </c>
-      <c r="L420" t="n">
+      <c r="L420" s="2" t="n">
         <v>47.24</v>
       </c>
-      <c r="M420" t="n">
+      <c r="M420" s="2" t="n">
         <v>22.23</v>
       </c>
-      <c r="N420" t="n">
+      <c r="N420" s="2" t="n">
         <v>18.43</v>
       </c>
-      <c r="O420" t="n">
+      <c r="O420" s="2" t="n">
         <v>36.16</v>
       </c>
-      <c r="P420" t="n">
+      <c r="P420" s="2" t="n">
         <v>28.19</v>
       </c>
-      <c r="Q420" t="n">
+      <c r="Q420" s="2" t="n">
         <v>16.98</v>
       </c>
-      <c r="R420" t="n">
+      <c r="R420" s="2" t="n">
         <v>35.91</v>
       </c>
-      <c r="S420" t="n">
+      <c r="S420" s="2" t="n">
         <v>19.31</v>
       </c>
-      <c r="T420" t="n">
+      <c r="T420" s="2" t="n">
         <v>101.43</v>
       </c>
-      <c r="U420" t="n">
+      <c r="U420" s="2" t="n">
         <v>27.51</v>
       </c>
-      <c r="V420" t="n">
+      <c r="V420" s="2" t="n">
         <v>25.34</v>
       </c>
-      <c r="W420" t="n">
+      <c r="W420" s="2" t="n">
         <v>16.03</v>
       </c>
-      <c r="X420" t="n">
+      <c r="X420" s="2" t="n">
         <v>20.43</v>
       </c>
-      <c r="Y420" t="n">
+      <c r="Y420" s="2" t="n">
         <v>81.59</v>
       </c>
-      <c r="Z420" t="n">
+      <c r="Z420" s="2" t="n">
         <v>8.84</v>
       </c>
-      <c r="AA420" t="n">
+      <c r="AA420" s="2" t="n">
         <v>9.880000000000001</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/31</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="C421" s="2" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="D421" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E421" s="2" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="F421" s="2" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="G421" s="2" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="H421" s="2" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="I421" s="2" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="J421" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="K421" s="2" t="n">
+        <v>29.54</v>
+      </c>
+      <c r="L421" s="2" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="N421" s="2" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="O421" s="2" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="P421" s="2" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="Q421" s="2" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="R421" s="2" t="n">
+        <v>36.24</v>
+      </c>
+      <c r="S421" s="2" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="T421" s="2" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="U421" s="2" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="V421" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="W421" s="2" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="X421" s="2" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="Y421" s="2" t="n">
+        <v>83.81999999999999</v>
+      </c>
+      <c r="Z421" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="AA421" s="2" t="n">
+        <v>10.03</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/01</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="C422" s="2" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="D422" s="2" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="E422" s="2" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="F422" s="2" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="G422" s="2" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="H422" s="2" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="I422" s="2" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="J422" s="2" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="K422" s="2" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="L422" s="2" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="M422" s="2" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="N422" s="2" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="O422" s="2" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="P422" s="2" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="Q422" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="R422" s="2" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="S422" s="2" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="T422" s="2" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="U422" s="2" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="V422" s="2" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="W422" s="2" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="X422" s="2" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="Y422" s="2" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="Z422" s="2" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AA422" s="2" t="n">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/02</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="C423" s="2" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="D423" s="2" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="E423" s="2" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="F423" s="2" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="G423" s="2" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="H423" s="2" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="I423" s="2" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="J423" s="2" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="K423" s="2" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="L423" s="2" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="O423" s="2" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="P423" s="2" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="Q423" s="2" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="R423" s="2" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="S423" s="2" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="T423" s="2" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="U423" s="2" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="V423" s="2" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="W423" s="2" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="X423" s="2" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="Y423" s="2" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="Z423" s="2" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="AA423" s="2" t="n">
+        <v>9.869999999999999</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/03</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="C424" s="2" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="D424" s="2" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="F424" s="2" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="G424" s="2" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="H424" s="2" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="I424" s="2" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="J424" s="2" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="K424" s="2" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="L424" s="2" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="O424" s="2" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="P424" s="2" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="Q424" s="2" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="R424" s="2" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="S424" s="2" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="T424" s="2" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="U424" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="V424" s="2" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="W424" s="2" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="X424" s="2" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="Y424" s="2" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="Z424" s="2" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="AA424" s="2" t="n">
+        <v>9.83</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/04</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="C425" s="2" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="D425" s="2" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="E425" s="2" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="F425" s="2" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="G425" s="2" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="H425" s="2" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="I425" s="2" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="J425" s="2" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="K425" s="2" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="L425" s="2" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="M425" s="2" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="O425" s="2" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="P425" s="2" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="Q425" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="R425" s="2" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="S425" s="2" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="T425" s="2" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="U425" s="2" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="V425" s="2" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="W425" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="X425" s="2" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="Y425" s="2" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="Z425" s="2" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AA425" s="2" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/07</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="C426" s="2" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="D426" s="2" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="E426" s="2" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="F426" s="2" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="G426" s="2" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H426" s="2" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I426" s="2" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="J426" s="2" t="n">
+        <v>50.88</v>
+      </c>
+      <c r="K426" s="2" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="L426" s="2" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="O426" s="2" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="P426" s="2" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="Q426" s="2" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="R426" s="2" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="S426" s="2" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="T426" s="2" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="U426" s="2" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="V426" s="2" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="W426" s="2" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="X426" s="2" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="Y426" s="2" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="Z426" s="2" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="AA426" s="2" t="n">
+        <v>9.77</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/08</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="F427" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G427" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H427" s="2" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="I427" s="2" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="J427" s="2" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="K427" s="2" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="L427" s="2" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="M427" s="2" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="O427" s="2" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="P427" s="2" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="Q427" s="2" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="R427" s="2" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="S427" s="2" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="T427" s="2" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="U427" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="V427" s="2" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="W427" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="X427" s="2" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="Y427" s="2" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="Z427" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA427" s="2" t="n">
+        <v>9.77</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/09</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="D428" s="2" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="F428" s="2" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="G428" s="2" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="H428" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="I428" s="2" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="J428" s="2" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="K428" s="2" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="L428" s="2" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="M428" s="2" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="O428" s="2" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="P428" s="2" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="Q428" s="2" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="R428" s="2" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="S428" s="2" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="T428" s="2" t="n">
+        <v>69.36</v>
+      </c>
+      <c r="U428" s="2" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="V428" s="2" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="W428" s="2" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="X428" s="2" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="Y428" s="2" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="Z428" s="2" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="AA428" s="2" t="n">
+        <v>9.82</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/10</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="C429" s="2" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="D429" s="2" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="F429" s="2" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="G429" s="2" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H429" s="2" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="I429" s="2" t="n">
+        <v>43.09</v>
+      </c>
+      <c r="J429" s="2" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="K429" s="2" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="L429" s="2" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="M429" s="2" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="O429" s="2" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="P429" s="2" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="Q429" s="2" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="R429" s="2" t="n">
+        <v>33.27</v>
+      </c>
+      <c r="S429" s="2" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="T429" s="2" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="U429" s="2" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="V429" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W429" s="2" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="X429" s="2" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="Y429" s="2" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="Z429" s="2" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="AA429" s="2" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/11</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="C430" s="2" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="D430" s="2" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E430" s="2" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="F430" s="2" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="G430" s="2" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="H430" s="2" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="I430" s="2" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="J430" s="2" t="n">
+        <v>48.88</v>
+      </c>
+      <c r="K430" s="2" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="L430" s="2" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="M430" s="2" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="N430" s="2" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="O430" s="2" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="P430" s="2" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="Q430" s="2" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="R430" s="2" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="S430" s="2" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="T430" s="2" t="n">
+        <v>68.17</v>
+      </c>
+      <c r="U430" s="2" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="V430" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="W430" s="2" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="X430" s="2" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="Y430" s="2" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="Z430" s="2" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="AA430" s="2" t="n">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/14</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="C431" s="2" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="D431" s="2" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="F431" s="2" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="G431" s="2" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="H431" s="2" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="I431" s="2" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="J431" s="2" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="K431" s="2" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="L431" s="2" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="M431" s="2" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="O431" s="2" t="n">
+        <v>31.31</v>
+      </c>
+      <c r="P431" s="2" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="Q431" s="2" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="R431" s="2" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="S431" s="2" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="T431" s="2" t="n">
+        <v>66.88</v>
+      </c>
+      <c r="U431" s="2" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="V431" s="2" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="W431" s="2" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="X431" s="2" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="Y431" s="2" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="Z431" s="2" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="AA431" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/15</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="C432" s="2" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="D432" s="2" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="E432" s="2" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="F432" s="2" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="G432" s="2" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="H432" s="2" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="I432" s="2" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="J432" s="2" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="K432" s="2" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="L432" s="2" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="M432" s="2" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="N432" s="2" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="O432" s="2" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="P432" s="2" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="Q432" s="2" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="R432" s="2" t="n">
+        <v>32.77</v>
+      </c>
+      <c r="S432" s="2" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="T432" s="2" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="U432" s="2" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="V432" s="2" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="W432" s="2" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="X432" s="2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y432" s="2" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="Z432" s="2" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="AA432" s="2" t="n">
+        <v>9.720000000000001</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/16</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="C433" s="2" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="D433" s="2" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="E433" s="2" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F433" s="2" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="G433" s="2" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="H433" s="2" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="I433" s="2" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="J433" s="2" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="K433" s="2" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="L433" s="2" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="M433" s="2" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="N433" s="2" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="O433" s="2" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="P433" s="2" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="Q433" s="2" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="R433" s="2" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="S433" s="2" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="T433" s="2" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="U433" s="2" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="V433" s="2" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="W433" s="2" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X433" s="2" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="Y433" s="2" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="Z433" s="2" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="AA433" s="2" t="n">
+        <v>9.67</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/17</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C434" s="2" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="D434" s="2" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="E434" s="2" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F434" s="2" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="G434" s="2" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="H434" s="2" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="I434" s="2" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="J434" s="2" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="K434" s="2" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="L434" s="2" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="M434" s="2" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N434" s="2" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="O434" s="2" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="P434" s="2" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="Q434" s="2" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="R434" s="2" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="S434" s="2" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="T434" s="2" t="n">
+        <v>70.56</v>
+      </c>
+      <c r="U434" s="2" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="V434" s="2" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="W434" s="2" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="X434" s="2" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="Y434" s="2" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="Z434" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA434" s="2" t="n">
+        <v>9.630000000000001</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/18</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C435" s="2" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="D435" s="2" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="E435" s="2" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="F435" s="2" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="G435" s="2" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="H435" s="2" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="I435" s="2" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="J435" s="2" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="K435" s="2" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="L435" s="2" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="M435" s="2" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="O435" s="2" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="P435" s="2" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="Q435" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="R435" s="2" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="S435" s="2" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="T435" s="2" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="U435" s="2" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="V435" s="2" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="W435" s="2" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="X435" s="2" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Y435" s="2" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="Z435" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA435" s="2" t="n">
+        <v>9.609999999999999</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/21</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="C436" s="2" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="D436" s="2" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="E436" s="2" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="F436" s="2" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="G436" s="2" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="H436" s="2" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="I436" s="2" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="J436" s="2" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="K436" s="2" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L436" s="2" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="M436" s="2" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O436" s="2" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="P436" s="2" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="Q436" s="2" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="R436" s="2" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="S436" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="T436" s="2" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="U436" s="2" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="V436" s="2" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="W436" s="2" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="X436" s="2" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="Y436" s="2" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="Z436" s="2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="AA436" s="2" t="n">
+        <v>9.67</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/22</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="C437" s="2" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="D437" s="2" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="E437" s="2" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="F437" s="2" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="G437" s="2" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="H437" s="2" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="I437" s="2" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="J437" s="2" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="K437" s="2" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="L437" s="2" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="M437" s="2" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="N437" s="2" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="O437" s="2" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="P437" s="2" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="Q437" s="2" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="R437" s="2" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="S437" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="T437" s="2" t="n">
+        <v>73.62</v>
+      </c>
+      <c r="U437" s="2" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="V437" s="2" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="W437" s="2" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="X437" s="2" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="Y437" s="2" t="n">
+        <v>61.21</v>
+      </c>
+      <c r="Z437" s="2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="AA437" s="2" t="n">
+        <v>9.69</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/23</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="C438" s="2" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="D438" s="2" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E438" s="2" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="F438" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G438" s="2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H438" s="2" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="I438" s="2" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="J438" s="2" t="n">
+        <v>53.39</v>
+      </c>
+      <c r="K438" s="2" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="L438" s="2" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="M438" s="2" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="O438" s="2" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="P438" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="Q438" s="2" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="R438" s="2" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="S438" s="2" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="T438" s="2" t="n">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="U438" s="2" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="V438" s="2" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="W438" s="2" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="X438" s="2" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="Y438" s="2" t="n">
+        <v>60.93</v>
+      </c>
+      <c r="Z438" s="2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AA438" s="2" t="n">
+        <v>9.640000000000001</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/24</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="C439" s="2" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="D439" s="2" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E439" s="2" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="F439" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="G439" s="2" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="H439" s="2" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="I439" s="2" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="J439" s="2" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="K439" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L439" s="2" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="M439" s="2" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="O439" s="2" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="P439" s="2" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="Q439" s="2" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="R439" s="2" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="S439" s="2" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="T439" s="2" t="n">
+        <v>71.56</v>
+      </c>
+      <c r="U439" s="2" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="V439" s="2" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="W439" s="2" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="X439" s="2" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="Y439" s="2" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="Z439" s="2" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="AA439" s="2" t="n">
+        <v>9.630000000000001</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/28</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="C440" s="2" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="D440" s="2" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="E440" s="2" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="F440" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G440" s="2" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="H440" s="2" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="I440" s="2" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="J440" s="2" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="K440" s="2" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="L440" s="2" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="M440" s="2" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="O440" s="2" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="P440" s="2" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="Q440" s="2" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="R440" s="2" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="S440" s="2" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="T440" s="2" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="U440" s="2" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="V440" s="2" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="W440" s="2" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="X440" s="2" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="Y440" s="2" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="Z440" s="2" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="AA440" s="2" t="n">
+        <v>9.630000000000001</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026/9/29</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="C441" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="D441" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="E441" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="F441" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="G441" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="H441" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="I441" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="J441" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="K441" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="L441" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="M441" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="N441" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="O441" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="P441" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="R441" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="S441" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="T441" t="n">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="U441" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="V441" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="W441" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="X441" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>9.619999999999999</v>
       </c>
     </row>
   </sheetData>
